--- a/results/class_sensitivity/hsp90_class_multivariable_model.xlsx
+++ b/results/class_sensitivity/hsp90_class_multivariable_model.xlsx
@@ -470,28 +470,28 @@
         <v>43</v>
       </c>
       <c r="B2" t="n">
-        <v>0.1042513275886747</v>
+        <v>0.08575529454961024</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02997754047158316</v>
+        <v>0.03151690414886438</v>
       </c>
       <c r="D2" t="n">
-        <v>0.000505834097057274</v>
+        <v>0.006509851651876862</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02560390434375413</v>
+        <v>0.01250223475451228</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3383444151334662</v>
+        <v>0.6445210375064898</v>
       </c>
       <c r="G2" t="n">
-        <v>0.156383724113193</v>
+        <v>0.1604405610067644</v>
       </c>
       <c r="H2" t="n">
-        <v>2.539003320818048e-06</v>
+        <v>7.263676316355445e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4999837329300657</v>
+        <v>0.5180965586990935</v>
       </c>
     </row>
   </sheetData>
@@ -557,13 +557,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3076923076923077</v>
+        <v>0.3205128205128205</v>
       </c>
       <c r="C2" t="n">
         <v>-0.1786272139903385</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.5005747545885065</v>
+        <v>-0.5005747545885066</v>
       </c>
       <c r="E2" t="n">
         <v>0.3461538461538461</v>
@@ -572,10 +572,10 @@
         <v>0.8662597807285108</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.074051322311229</v>
+        <v>-1.07405132231123</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.041708678044114</v>
+        <v>-1.0428598987716</v>
       </c>
     </row>
     <row r="3">
@@ -600,10 +600,10 @@
         <v>0.5409938465164948</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.182718133083967</v>
+        <v>-2.182718133083968</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.071059906491502</v>
+        <v>-1.07225652356221</v>
       </c>
     </row>
     <row r="4">
@@ -613,13 +613,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6499999999999999</v>
       </c>
       <c r="C4" t="n">
         <v>-0.2094323762561981</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5621957635480659</v>
+        <v>0.5621957635480657</v>
       </c>
       <c r="E4" t="n">
         <v>0.5333333333333333</v>
@@ -628,10 +628,10 @@
         <v>-0.1862927561955771</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7914460542124923</v>
+        <v>0.7914460542124919</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1296010118630093</v>
+        <v>0.1302614078723462</v>
       </c>
     </row>
     <row r="5">
@@ -647,7 +647,7 @@
         <v>-0.2595319632042399</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3126084452908054</v>
+        <v>0.3126084452908055</v>
       </c>
       <c r="E5" t="n">
         <v>0.5116279069767442</v>
@@ -656,10 +656,10 @@
         <v>-1.898098293394519</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3533416097658337</v>
+        <v>0.353341609765834</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.006224641888565128</v>
+        <v>-0.005774321856355832</v>
       </c>
     </row>
     <row r="6">
@@ -675,7 +675,7 @@
         <v>-0.1656382046631881</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.07965150685765063</v>
+        <v>-0.07965150685765061</v>
       </c>
       <c r="E6" t="n">
         <v>0.7209302325581395</v>
@@ -684,10 +684,10 @@
         <v>1.310068990413297</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.3351982952847029</v>
+        <v>-0.335198295284703</v>
       </c>
       <c r="H6" t="n">
-        <v>1.303522733573047</v>
+        <v>1.305998786241844</v>
       </c>
     </row>
     <row r="7">
@@ -703,7 +703,7 @@
         <v>-0.1799067898613997</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7291156282151543</v>
+        <v>0.7291156282151536</v>
       </c>
       <c r="E7" t="n">
         <v>0.4</v>
@@ -712,10 +712,10 @@
         <v>0.8225391595660956</v>
       </c>
       <c r="G7" t="n">
-        <v>1.084443050565126</v>
+        <v>1.084443050565125</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.7047565754680917</v>
+        <v>-0.7053866461753959</v>
       </c>
     </row>
     <row r="8">
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6793381037567083</v>
+        <v>0.6279069767441861</v>
       </c>
       <c r="C8" t="n">
         <v>-0.2183080445642374</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5519547653573037</v>
+        <v>0.5519547653573036</v>
       </c>
       <c r="E8" t="n">
         <v>0.3333333333333333</v>
@@ -740,10 +740,10 @@
         <v>-0.4895570959155838</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7734698731538115</v>
+        <v>0.7734698731538113</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.121935369133642</v>
+        <v>-1.123210673199267</v>
       </c>
     </row>
     <row r="9">
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6</v>
+        <v>0.5391472868217054</v>
       </c>
       <c r="C9" t="n">
         <v>-0.1662653967408163</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0971929910513588</v>
+        <v>-0.09719299105135877</v>
       </c>
       <c r="E9" t="n">
         <v>0.5172413793103449</v>
@@ -768,10 +768,10 @@
         <v>1.288639055821527</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.3659891312979858</v>
+        <v>-0.3659891312979859</v>
       </c>
       <c r="H9" t="n">
-        <v>0.02890268235753184</v>
+        <v>0.02940733238382587</v>
       </c>
     </row>
     <row r="10">
@@ -787,7 +787,7 @@
         <v>-0.2152350766343056</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3276794542214613</v>
+        <v>0.3276794542214616</v>
       </c>
       <c r="E10" t="n">
         <v>0.3765227021040974</v>
@@ -796,10 +796,10 @@
         <v>-0.3845597528527057</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3797959826919853</v>
+        <v>0.3797959826919857</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.8516700376891828</v>
+        <v>-0.852527333432972</v>
       </c>
     </row>
     <row r="11">
@@ -824,10 +824,10 @@
         <v>0.6704960740005447</v>
       </c>
       <c r="G11" t="n">
-        <v>0.06139984176562876</v>
+        <v>0.06139984176562862</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.04260651342916554</v>
+        <v>-0.04221246374797257</v>
       </c>
     </row>
     <row r="12">
@@ -843,7 +843,7 @@
         <v>-0.2331316047101898</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2484970233722821</v>
+        <v>0.2484970233722822</v>
       </c>
       <c r="E12" t="n">
         <v>0.2093023255813954</v>
@@ -852,10 +852,10 @@
         <v>-0.9960493423518518</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2408058484201833</v>
+        <v>0.2408058484201835</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.898081961999783</v>
+        <v>-1.900557700220423</v>
       </c>
     </row>
     <row r="13">
@@ -865,13 +865,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7897435897435897</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="C13" t="n">
         <v>-0.2235656201793519</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2706101897207878</v>
+        <v>0.2706101897207877</v>
       </c>
       <c r="E13" t="n">
         <v>0.6333333333333333</v>
@@ -880,10 +880,10 @@
         <v>-0.6691982386565184</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2796214281768554</v>
+        <v>0.2796214281768553</v>
       </c>
       <c r="H13" t="n">
-        <v>0.7553692023613351</v>
+        <v>0.7569974484081529</v>
       </c>
     </row>
     <row r="14">
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.7441860465116279</v>
+        <v>0.772093023255814</v>
       </c>
       <c r="C14" t="n">
         <v>-0.2064610311547386</v>
@@ -908,10 +908,10 @@
         <v>-0.08476766771765566</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.278710873490573</v>
+        <v>-1.278710873490574</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3381904086957845</v>
+        <v>0.3391734213842818</v>
       </c>
     </row>
     <row r="15">
@@ -921,13 +921,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2583333333333333</v>
+        <v>0.3</v>
       </c>
       <c r="C15" t="n">
         <v>-0.2082082076743421</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.5491471363354226</v>
+        <v>-0.5491471363354224</v>
       </c>
       <c r="E15" t="n">
         <v>0.5</v>
@@ -939,7 +939,7 @@
         <v>-1.159311168321312</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.07898838496976594</v>
+        <v>-0.07865060563958931</v>
       </c>
     </row>
     <row r="16">
@@ -955,7 +955,7 @@
         <v>-0.1936907867929881</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6717746308695767</v>
+        <v>0.6717746308695768</v>
       </c>
       <c r="E16" t="n">
         <v>0.7857142857142857</v>
@@ -964,10 +964,10 @@
         <v>0.3515667681829672</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9837915192232654</v>
+        <v>0.9837915192232657</v>
       </c>
       <c r="H16" t="n">
-        <v>1.708920730739736</v>
+        <v>1.712023795891287</v>
       </c>
     </row>
     <row r="17">
@@ -992,10 +992,10 @@
         <v>-0.1735063372934399</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7214258945409769</v>
+        <v>0.7214258945409771</v>
       </c>
       <c r="H17" t="n">
-        <v>1.724512961399994</v>
+        <v>1.727640142416266</v>
       </c>
     </row>
     <row r="18">
@@ -1005,13 +1005,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6976744186046512</v>
+        <v>0.7626303127506014</v>
       </c>
       <c r="C18" t="n">
         <v>-0.1414054398988475</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.175688720659256</v>
+        <v>-1.175688720659255</v>
       </c>
       <c r="E18" t="n">
         <v>0.4333333333333333</v>
@@ -1023,7 +1023,7 @@
         <v>-2.259089212492582</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.4961671786353165</v>
+        <v>-0.4964746326634604</v>
       </c>
     </row>
     <row r="19">
@@ -1033,25 +1033,25 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7666666666666667</v>
+        <v>0.7404761904761905</v>
       </c>
       <c r="C19" t="n">
         <v>-0.1783653544666676</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2243907605925614</v>
+        <v>0.2243907605925616</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6511627906976745</v>
+        <v>0.6525044722719142</v>
       </c>
       <c r="F19" t="n">
         <v>0.8752070118314944</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1984917559553211</v>
+        <v>0.1984917559553215</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8669402750858433</v>
+        <v>0.8771498855174332</v>
       </c>
     </row>
     <row r="20">
@@ -1061,13 +1061,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.2142857142857143</v>
+        <v>0.2562015503875969</v>
       </c>
       <c r="C20" t="n">
         <v>-0.2272999068630794</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6352947061356088</v>
+        <v>0.6352947061356089</v>
       </c>
       <c r="E20" t="n">
         <v>0.3666666666666666</v>
@@ -1076,10 +1076,10 @@
         <v>-0.7967915585240548</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9197577483144506</v>
+        <v>0.9197577483144507</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.9133459723008672</v>
+        <v>-0.9142986596873318</v>
       </c>
     </row>
     <row r="21">
@@ -1104,10 +1104,10 @@
         <v>0.042647472440717</v>
       </c>
       <c r="G21" t="n">
-        <v>0.06922065205435446</v>
+        <v>0.06922065205435443</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7553692023613351</v>
+        <v>0.7569974484081529</v>
       </c>
     </row>
     <row r="22">
@@ -1117,13 +1117,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.1162790697674419</v>
+        <v>0.2</v>
       </c>
       <c r="C22" t="n">
         <v>-0.2357862821744499</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5200865441756435</v>
+        <v>0.5200865441756433</v>
       </c>
       <c r="E22" t="n">
         <v>0.3571428571428572</v>
@@ -1132,10 +1132,10 @@
         <v>-1.086754512985503</v>
       </c>
       <c r="G22" t="n">
-        <v>0.7175310961607286</v>
+        <v>0.7175310961607283</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.9729429428245171</v>
+        <v>-0.9739878064050276</v>
       </c>
     </row>
     <row r="23">
@@ -1145,13 +1145,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.4523809523809524</v>
+        <v>0.296551724137931</v>
       </c>
       <c r="C23" t="n">
         <v>-0.1928960493937777</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.09948607968653907</v>
+        <v>-0.09948607968653904</v>
       </c>
       <c r="E23" t="n">
         <v>0.4</v>
@@ -1160,10 +1160,10 @@
         <v>0.3787214008548575</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.3700142249189168</v>
+        <v>-0.3700142249189169</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.7047565754680917</v>
+        <v>-0.7053866461753959</v>
       </c>
     </row>
     <row r="24">
@@ -1173,13 +1173,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6923076923076923</v>
+        <v>0.6252236135957066</v>
       </c>
       <c r="C24" t="n">
         <v>-0.1891070006869582</v>
       </c>
       <c r="D24" t="n">
-        <v>0.4650466426225435</v>
+        <v>0.4650466426225436</v>
       </c>
       <c r="E24" t="n">
         <v>0.6666666666666666</v>
@@ -1188,10 +1188,10 @@
         <v>0.5081858326430231</v>
       </c>
       <c r="G24" t="n">
-        <v>0.6209187135257058</v>
+        <v>0.620918713525706</v>
       </c>
       <c r="H24" t="n">
-        <v>0.9639585991941103</v>
+        <v>0.9659094619200884</v>
       </c>
     </row>
     <row r="25">
@@ -1201,13 +1201,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7690476190476191</v>
+        <v>0.6511627906976745</v>
       </c>
       <c r="C25" t="n">
         <v>-0.1679123265606992</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.09730409846625709</v>
+        <v>-0.09730409846625707</v>
       </c>
       <c r="E25" t="n">
         <v>0.5</v>
@@ -1216,10 +1216,10 @@
         <v>1.232366664035595</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.3661841598459817</v>
+        <v>-0.3661841598459818</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.07898838496976594</v>
+        <v>-0.07865060563958931</v>
       </c>
     </row>
     <row r="26">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.4666666666666667</v>
+        <v>0.4775193798449612</v>
       </c>
       <c r="C26" t="n">
         <v>-0.2002121226750436</v>
@@ -1244,10 +1244,10 @@
         <v>0.128745392741009</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.4177960842046976</v>
+        <v>-0.4177960842046977</v>
       </c>
       <c r="H26" t="n">
-        <v>0.3381904086957845</v>
+        <v>0.3391734213842818</v>
       </c>
     </row>
     <row r="27">
@@ -1263,19 +1263,19 @@
         <v>-0.2539667075870732</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1079673091236757</v>
+        <v>0.1079673091236756</v>
       </c>
       <c r="E27" t="n">
-        <v>0.462962962962963</v>
+        <v>0.4642857142857143</v>
       </c>
       <c r="F27" t="n">
         <v>-1.707944322838364</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.005868112496668865</v>
+        <v>-0.005868112496669061</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.3107543814506274</v>
+        <v>-0.3024849058309488</v>
       </c>
     </row>
     <row r="28">
@@ -1285,13 +1285,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.1785714285714286</v>
+        <v>0.1726190476190476</v>
       </c>
       <c r="C28" t="n">
         <v>-0.1820048265378515</v>
       </c>
       <c r="D28" t="n">
-        <v>0.3034285964322371</v>
+        <v>0.303428596432237</v>
       </c>
       <c r="E28" t="n">
         <v>0.396551724137931</v>
@@ -1300,10 +1300,10 @@
         <v>0.7508533230397119</v>
       </c>
       <c r="G28" t="n">
-        <v>0.3372280803911482</v>
+        <v>0.337228080391148</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.7263347889335512</v>
+        <v>-0.726998233780079</v>
       </c>
     </row>
     <row r="29">
@@ -1328,10 +1328,10 @@
         <v>2.614328938281727</v>
       </c>
       <c r="G29" t="n">
-        <v>-3.043802353806849</v>
+        <v>-3.043802353806848</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.5259656638971417</v>
+        <v>-0.5263192060223086</v>
       </c>
     </row>
     <row r="30">
@@ -1341,25 +1341,25 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.3928571428571428</v>
+        <v>0.3964285714285715</v>
       </c>
       <c r="C30" t="n">
         <v>-0.1998464016445489</v>
       </c>
       <c r="D30" t="n">
-        <v>0.3053439041445652</v>
+        <v>0.305343904144565</v>
       </c>
       <c r="E30" t="n">
-        <v>0.3908730158730159</v>
+        <v>0.3888888888888889</v>
       </c>
       <c r="F30" t="n">
         <v>0.1412413697182284</v>
       </c>
       <c r="G30" t="n">
-        <v>0.3405900493690311</v>
+        <v>0.3405900493690308</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.7618703388865898</v>
+        <v>-0.7750239840127079</v>
       </c>
     </row>
     <row r="31">
@@ -1369,7 +1369,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.8023255813953489</v>
+        <v>0.7666666666666667</v>
       </c>
       <c r="C31" t="n">
         <v>-0.205184187788136</v>
@@ -1384,10 +1384,10 @@
         <v>-0.04114041092304525</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.02995177910962615</v>
+        <v>-0.0299517791096262</v>
       </c>
       <c r="H31" t="n">
-        <v>0.4023717615674075</v>
+        <v>0.4034540409264156</v>
       </c>
     </row>
     <row r="32">
@@ -1397,13 +1397,13 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.7857142857142857</v>
+        <v>0.7998338870431894</v>
       </c>
       <c r="C32" t="n">
         <v>-0.184285453771279</v>
       </c>
       <c r="D32" t="n">
-        <v>0.08387376478049795</v>
+        <v>0.08387376478049799</v>
       </c>
       <c r="E32" t="n">
         <v>0.6666666666666666</v>
@@ -1412,10 +1412,10 @@
         <v>0.6729287219743062</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.04815988009496807</v>
+        <v>-0.04815988009496806</v>
       </c>
       <c r="H32" t="n">
-        <v>0.9639585991941103</v>
+        <v>0.9659094619200884</v>
       </c>
     </row>
     <row r="33">
@@ -1425,7 +1425,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.2452934662236988</v>
+        <v>0.2884615384615384</v>
       </c>
       <c r="C33" t="n">
         <v>-0.194595351118395</v>
@@ -1440,10 +1440,10 @@
         <v>0.3206595628483209</v>
       </c>
       <c r="G33" t="n">
-        <v>0.002241643379861103</v>
+        <v>0.00224164337986103</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.7047565754680917</v>
+        <v>-0.7053866461753959</v>
       </c>
     </row>
     <row r="34">
@@ -1471,7 +1471,7 @@
         <v>1.495321218343896</v>
       </c>
       <c r="H34" t="n">
-        <v>-1.121935369133642</v>
+        <v>-1.123210673199267</v>
       </c>
     </row>
     <row r="35">
@@ -1481,7 +1481,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.8418604651162791</v>
+        <v>0.9615384615384616</v>
       </c>
       <c r="C35" t="n">
         <v>-0.226134911817538</v>
@@ -1490,7 +1490,7 @@
         <v>0.3468781549400004</v>
       </c>
       <c r="E35" t="n">
-        <v>0.9285714285714286</v>
+        <v>0.9259259259259259</v>
       </c>
       <c r="F35" t="n">
         <v>-0.7569859415269478</v>
@@ -1499,7 +1499,7 @@
         <v>0.4134957562667132</v>
       </c>
       <c r="H35" t="n">
-        <v>2.602875288594488</v>
+        <v>2.590780678124032</v>
       </c>
     </row>
     <row r="36">
@@ -1509,25 +1509,25 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.1904761904761905</v>
+        <v>0.2870879120879121</v>
       </c>
       <c r="C36" t="n">
         <v>-0.222738672149269</v>
       </c>
       <c r="D36" t="n">
-        <v>0.4892301648054121</v>
+        <v>0.4892301648054123</v>
       </c>
       <c r="E36" t="n">
-        <v>0.3232142857142857</v>
+        <v>0.325</v>
       </c>
       <c r="F36" t="n">
         <v>-0.6409430313163919</v>
       </c>
       <c r="G36" t="n">
-        <v>0.6633684206048471</v>
+        <v>0.6633684206048476</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.18525715031502</v>
+        <v>-1.175438676577251</v>
       </c>
     </row>
     <row r="37">
@@ -1543,7 +1543,7 @@
         <v>-0.2189178803002914</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.6142141682406723</v>
+        <v>-0.6142141682406718</v>
       </c>
       <c r="E37" t="n">
         <v>0.4285714285714285</v>
@@ -1552,10 +1552,10 @@
         <v>-0.5103939980409772</v>
       </c>
       <c r="G37" t="n">
-        <v>-1.27352432652056</v>
+        <v>-1.273524326520559</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.5259656638971417</v>
+        <v>-0.5263192060223086</v>
       </c>
     </row>
     <row r="38">
@@ -1571,7 +1571,7 @@
         <v>-0.2258584547941442</v>
       </c>
       <c r="D38" t="n">
-        <v>0.2233539459840137</v>
+        <v>0.2233539459840138</v>
       </c>
       <c r="E38" t="n">
         <v>0.5348837209302325</v>
@@ -1580,10 +1580,10 @@
         <v>-0.747539942222924</v>
       </c>
       <c r="G38" t="n">
-        <v>0.1966718193846505</v>
+        <v>0.1966718193846507</v>
       </c>
       <c r="H38" t="n">
-        <v>0.1393028442738358</v>
+        <v>0.1399782457101104</v>
       </c>
     </row>
     <row r="39">
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.2012820512820513</v>
       </c>
       <c r="C39" t="n">
         <v>-0.2418526659406501</v>
@@ -1608,10 +1608,10 @@
         <v>-1.294031058648946</v>
       </c>
       <c r="G39" t="n">
-        <v>1.814444165194628</v>
+        <v>1.814444165194629</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.4961671786353165</v>
+        <v>-0.4964746326634604</v>
       </c>
     </row>
     <row r="40">
@@ -1627,7 +1627,7 @@
         <v>-0.2522460594059376</v>
       </c>
       <c r="D40" t="n">
-        <v>0.7264631840168821</v>
+        <v>0.726463184016882</v>
       </c>
       <c r="E40" t="n">
         <v>0.813953488372093</v>
@@ -1639,7 +1639,7 @@
         <v>1.079787174617487</v>
       </c>
       <c r="H40" t="n">
-        <v>1.885632678222652</v>
+        <v>1.889009056507711</v>
       </c>
     </row>
     <row r="41">
@@ -1649,13 +1649,13 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.7</v>
+        <v>0.643103448275862</v>
       </c>
       <c r="C41" t="n">
         <v>-0.2392060740558485</v>
       </c>
       <c r="D41" t="n">
-        <v>0.7212295494574288</v>
+        <v>0.7212295494574285</v>
       </c>
       <c r="E41" t="n">
         <v>0.6</v>
@@ -1667,7 +1667,7 @@
         <v>1.070600495674357</v>
       </c>
       <c r="H41" t="n">
-        <v>0.5467798055285598</v>
+        <v>0.5480854348962173</v>
       </c>
     </row>
     <row r="42">
@@ -1677,25 +1677,25 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.5952380952380952</v>
+        <v>0.692970822281167</v>
       </c>
       <c r="C42" t="n">
         <v>-0.2246998597349494</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.5988724484970279</v>
+        <v>-0.5988724484970276</v>
       </c>
       <c r="E42" t="n">
-        <v>0.7113095238095238</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="F42" t="n">
         <v>-0.7079530003234276</v>
       </c>
       <c r="G42" t="n">
-        <v>-1.246594770755961</v>
+        <v>-1.24659477075596</v>
       </c>
       <c r="H42" t="n">
-        <v>1.243319398523721</v>
+        <v>1.227049478810008</v>
       </c>
     </row>
     <row r="43">
@@ -1720,10 +1720,10 @@
         <v>-0.2712739036722548</v>
       </c>
       <c r="G43" t="n">
-        <v>0.07214911180536854</v>
+        <v>0.07214911180536859</v>
       </c>
       <c r="H43" t="n">
-        <v>-1.170444531187776</v>
+        <v>-1.171794862388089</v>
       </c>
     </row>
     <row r="44">
@@ -1733,13 +1733,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.8</v>
+        <v>0.8069767441860465</v>
       </c>
       <c r="C44" t="n">
         <v>-0.1611385731101388</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.01652716774940665</v>
+        <v>-0.01652716774940664</v>
       </c>
       <c r="E44" t="n">
         <v>0.6428571428571429</v>
@@ -1751,7 +1751,7 @@
         <v>-0.2243951755221257</v>
       </c>
       <c r="H44" t="n">
-        <v>0.8149661728849856</v>
+        <v>0.8166865951258493</v>
       </c>
     </row>
   </sheetData>
@@ -1812,22 +1812,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5168432297826566</v>
+        <v>0.5187685627378099</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02817890619356865</v>
+        <v>0.02686927190204854</v>
       </c>
       <c r="D2" t="n">
-        <v>18.3414936773031</v>
+        <v>19.3071313814893</v>
       </c>
       <c r="E2" t="n">
-        <v>3.860430750631225e-75</v>
+        <v>4.678468676311012e-83</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4616135885195294</v>
+        <v>0.4661057575189808</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5720728710457839</v>
+        <v>0.5714313679566391</v>
       </c>
     </row>
     <row r="3">
@@ -1837,22 +1837,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1042513275886747</v>
+        <v>0.08575529454961024</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02997754047158316</v>
+        <v>0.03151690414886438</v>
       </c>
       <c r="D3" t="n">
-        <v>3.477647797273376</v>
+        <v>2.720930144171542</v>
       </c>
       <c r="E3" t="n">
-        <v>0.000505834097057274</v>
+        <v>0.006509851651876862</v>
       </c>
       <c r="F3" t="n">
-        <v>0.04549642791927979</v>
+        <v>0.02398329751363504</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1630062272580695</v>
+        <v>0.1475272915855854</v>
       </c>
     </row>
     <row r="4">
@@ -1862,22 +1862,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02560390434375413</v>
+        <v>0.01250223475451228</v>
       </c>
       <c r="C4" t="n">
-        <v>0.02674200141871803</v>
+        <v>0.02709707263596434</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9574415894628105</v>
+        <v>0.461386915202006</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3383444151334662</v>
+        <v>0.6445210375064898</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.02680945531145225</v>
+        <v>-0.04060705169844367</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0780172639989605</v>
+        <v>0.06561152120746822</v>
       </c>
     </row>
     <row r="5">
@@ -1887,22 +1887,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.156383724113193</v>
+        <v>0.1604405610067644</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03323796861114896</v>
+        <v>0.0323849016354711</v>
       </c>
       <c r="D5" t="n">
-        <v>4.704972374898311</v>
+        <v>4.954177808310346</v>
       </c>
       <c r="E5" t="n">
-        <v>2.539003320818048e-06</v>
+        <v>7.263676316355445e-07</v>
       </c>
       <c r="F5" t="n">
-        <v>0.09123850271606829</v>
+        <v>0.09696732015836873</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2215289455103178</v>
+        <v>0.22391380185516</v>
       </c>
     </row>
   </sheetData>

--- a/results/class_sensitivity/hsp90_class_multivariable_model.xlsx
+++ b/results/class_sensitivity/hsp90_class_multivariable_model.xlsx
@@ -470,28 +470,28 @@
         <v>43</v>
       </c>
       <c r="B2" t="n">
-        <v>0.08575529454961024</v>
+        <v>0.09564380672158018</v>
       </c>
       <c r="C2" t="n">
-        <v>0.03151690414886438</v>
+        <v>0.03123686201353519</v>
       </c>
       <c r="D2" t="n">
-        <v>0.006509851651876862</v>
+        <v>0.002199449383018057</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01250223475451228</v>
+        <v>0.01564928838417697</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6445210375064898</v>
+        <v>0.5844097660152567</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1604405610067644</v>
+        <v>0.160252927582874</v>
       </c>
       <c r="H2" t="n">
-        <v>7.263676316355445e-07</v>
+        <v>9.759578852709117e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5180965586990935</v>
+        <v>0.5094828024649158</v>
       </c>
     </row>
   </sheetData>
@@ -557,13 +557,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3205128205128205</v>
+        <v>0.2701252236135957</v>
       </c>
       <c r="C2" t="n">
         <v>-0.1786272139903385</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.5005747545885066</v>
+        <v>-0.5005747545885065</v>
       </c>
       <c r="E2" t="n">
         <v>0.3461538461538461</v>
@@ -572,10 +572,10 @@
         <v>0.8662597807285108</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.07405132231123</v>
+        <v>-1.074051322311229</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.0428598987716</v>
+        <v>-1.040406032928116</v>
       </c>
     </row>
     <row r="3">
@@ -603,7 +603,7 @@
         <v>-2.182718133083968</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.07225652356221</v>
+        <v>-1.069774074986583</v>
       </c>
     </row>
     <row r="4">
@@ -613,13 +613,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6499999999999999</v>
+        <v>0.6821705426356589</v>
       </c>
       <c r="C4" t="n">
         <v>-0.2094323762561981</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5621957635480657</v>
+        <v>0.5621957635480654</v>
       </c>
       <c r="E4" t="n">
         <v>0.5333333333333333</v>
@@ -628,10 +628,10 @@
         <v>-0.1862927561955771</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7914460542124919</v>
+        <v>0.7914460542124914</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1302614078723462</v>
+        <v>0.1315746321517874</v>
       </c>
     </row>
     <row r="5">
@@ -647,7 +647,7 @@
         <v>-0.2595319632042399</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3126084452908055</v>
+        <v>0.3126084452908053</v>
       </c>
       <c r="E5" t="n">
         <v>0.5116279069767442</v>
@@ -656,10 +656,10 @@
         <v>-1.898098293394519</v>
       </c>
       <c r="G5" t="n">
-        <v>0.353341609765834</v>
+        <v>0.3533416097658336</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.005774321856355832</v>
+        <v>-0.004328828214279531</v>
       </c>
     </row>
     <row r="6">
@@ -675,7 +675,7 @@
         <v>-0.1656382046631881</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.07965150685765061</v>
+        <v>-0.07965150685765064</v>
       </c>
       <c r="E6" t="n">
         <v>0.7209302325581395</v>
@@ -684,10 +684,10 @@
         <v>1.310068990413297</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.335198295284703</v>
+        <v>-0.3351982952847029</v>
       </c>
       <c r="H6" t="n">
-        <v>1.305998786241844</v>
+        <v>1.306168825315653</v>
       </c>
     </row>
     <row r="7">
@@ -703,7 +703,7 @@
         <v>-0.1799067898613997</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7291156282151536</v>
+        <v>0.7291156282151543</v>
       </c>
       <c r="E7" t="n">
         <v>0.4</v>
@@ -712,10 +712,10 @@
         <v>0.8225391595660956</v>
       </c>
       <c r="G7" t="n">
-        <v>1.084443050565125</v>
+        <v>1.084443050565126</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.7053866461753959</v>
+        <v>-0.7032609100969104</v>
       </c>
     </row>
     <row r="8">
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6279069767441861</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="C8" t="n">
         <v>-0.2183080445642374</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5519547653573036</v>
+        <v>0.5519547653573037</v>
       </c>
       <c r="E8" t="n">
         <v>0.3333333333333333</v>
@@ -740,10 +740,10 @@
         <v>-0.4895570959155838</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7734698731538113</v>
+        <v>0.7734698731538114</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.123210673199267</v>
+        <v>-1.12067868122126</v>
       </c>
     </row>
     <row r="9">
@@ -753,16 +753,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5391472868217054</v>
+        <v>0.5833333333333333</v>
       </c>
       <c r="C9" t="n">
         <v>-0.1662653967408163</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.09719299105135877</v>
+        <v>-0.09719299105135884</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5172413793103449</v>
+        <v>0.5144346431435445</v>
       </c>
       <c r="F9" t="n">
         <v>1.288639055821527</v>
@@ -771,7 +771,7 @@
         <v>-0.3659891312979859</v>
       </c>
       <c r="H9" t="n">
-        <v>0.02940733238382587</v>
+        <v>0.0132448951089185</v>
       </c>
     </row>
     <row r="10">
@@ -799,7 +799,7 @@
         <v>0.3797959826919857</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.852527333432972</v>
+        <v>-0.8502585304928608</v>
       </c>
     </row>
     <row r="11">
@@ -824,10 +824,10 @@
         <v>0.6704960740005447</v>
       </c>
       <c r="G11" t="n">
-        <v>0.06139984176562862</v>
+        <v>0.06139984176562871</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.04221246374797257</v>
+        <v>-0.04073154081233329</v>
       </c>
     </row>
     <row r="12">
@@ -843,7 +843,7 @@
         <v>-0.2331316047101898</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2484970233722822</v>
+        <v>0.2484970233722821</v>
       </c>
       <c r="E12" t="n">
         <v>0.2093023255813954</v>
@@ -852,10 +852,10 @@
         <v>-0.9960493423518518</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2408058484201835</v>
+        <v>0.2408058484201833</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.900557700220423</v>
+        <v>-1.897269883313071</v>
       </c>
     </row>
     <row r="13">
@@ -880,10 +880,10 @@
         <v>-0.6691982386565184</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2796214281768553</v>
+        <v>0.2796214281768552</v>
       </c>
       <c r="H13" t="n">
-        <v>0.7569974484081529</v>
+        <v>0.7577012888383108</v>
       </c>
     </row>
     <row r="14">
@@ -899,7 +899,7 @@
         <v>-0.2064610311547386</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.6171689347710507</v>
+        <v>-0.6171689347710508</v>
       </c>
       <c r="E14" t="n">
         <v>0.5666666666666667</v>
@@ -911,7 +911,7 @@
         <v>-1.278710873490574</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3391734213842818</v>
+        <v>0.3402835177139619</v>
       </c>
     </row>
     <row r="15">
@@ -921,13 +921,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.3</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="C15" t="n">
         <v>-0.2082082076743421</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.5491471363354224</v>
+        <v>-0.5491471363354223</v>
       </c>
       <c r="E15" t="n">
         <v>0.5</v>
@@ -939,7 +939,7 @@
         <v>-1.159311168321312</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.07865060563958931</v>
+        <v>-0.07713425341038704</v>
       </c>
     </row>
     <row r="16">
@@ -955,7 +955,7 @@
         <v>-0.1936907867929881</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6717746308695768</v>
+        <v>0.6717746308695771</v>
       </c>
       <c r="E16" t="n">
         <v>0.7857142857142857</v>
@@ -964,10 +964,10 @@
         <v>0.3515667681829672</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9837915192232657</v>
+        <v>0.9837915192232661</v>
       </c>
       <c r="H16" t="n">
-        <v>1.712023795891287</v>
+        <v>1.711799051408252</v>
       </c>
     </row>
     <row r="17">
@@ -983,7 +983,7 @@
         <v>-0.2090581548323149</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5223054038452976</v>
+        <v>0.5223054038452978</v>
       </c>
       <c r="E17" t="n">
         <v>0.7882059800664452</v>
@@ -992,10 +992,10 @@
         <v>-0.1735063372934399</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7214258945409771</v>
+        <v>0.7214258945409773</v>
       </c>
       <c r="H17" t="n">
-        <v>1.727640142416266</v>
+        <v>1.727400213950274</v>
       </c>
     </row>
     <row r="18">
@@ -1005,7 +1005,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7626303127506014</v>
+        <v>0.7655038759689923</v>
       </c>
       <c r="C18" t="n">
         <v>-0.1414054398988475</v>
@@ -1023,7 +1023,7 @@
         <v>-2.259089212492582</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.4964746326634604</v>
+        <v>-0.494552024534736</v>
       </c>
     </row>
     <row r="19">
@@ -1033,25 +1033,25 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7404761904761905</v>
+        <v>0.7670542635658915</v>
       </c>
       <c r="C19" t="n">
         <v>-0.1783653544666676</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2243907605925616</v>
+        <v>0.2243907605925615</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6525044722719142</v>
+        <v>0.6470099667774087</v>
       </c>
       <c r="F19" t="n">
         <v>0.8752070118314944</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1984917559553215</v>
+        <v>0.1984917559553212</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8771498855174332</v>
+        <v>0.8433343365689713</v>
       </c>
     </row>
     <row r="20">
@@ -1061,7 +1061,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.2562015503875969</v>
+        <v>0.2238095238095238</v>
       </c>
       <c r="C20" t="n">
         <v>-0.2272999068630794</v>
@@ -1076,10 +1076,10 @@
         <v>-0.7967915585240548</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9197577483144507</v>
+        <v>0.9197577483144506</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.9142986596873318</v>
+        <v>-0.9119697956590852</v>
       </c>
     </row>
     <row r="21">
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.4418604651162791</v>
+        <v>0.5116279069767442</v>
       </c>
       <c r="C21" t="n">
         <v>-0.2027319592747009</v>
@@ -1104,10 +1104,10 @@
         <v>0.042647472440717</v>
       </c>
       <c r="G21" t="n">
-        <v>0.06922065205435443</v>
+        <v>0.06922065205435446</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7569974484081529</v>
+        <v>0.7577012888383108</v>
       </c>
     </row>
     <row r="22">
@@ -1117,13 +1117,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.2</v>
+        <v>0.1581395348837209</v>
       </c>
       <c r="C22" t="n">
         <v>-0.2357862821744499</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5200865441756433</v>
+        <v>0.5200865441756434</v>
       </c>
       <c r="E22" t="n">
         <v>0.3571428571428572</v>
@@ -1132,10 +1132,10 @@
         <v>-1.086754512985503</v>
       </c>
       <c r="G22" t="n">
-        <v>0.7175310961607283</v>
+        <v>0.7175310961607284</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.9739878064050276</v>
+        <v>-0.9716009058197063</v>
       </c>
     </row>
     <row r="23">
@@ -1145,13 +1145,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.296551724137931</v>
+        <v>0.3761904761904762</v>
       </c>
       <c r="C23" t="n">
         <v>-0.1928960493937777</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.09948607968653904</v>
+        <v>-0.099486079686539</v>
       </c>
       <c r="E23" t="n">
         <v>0.4</v>
@@ -1160,10 +1160,10 @@
         <v>0.3787214008548575</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.3700142249189169</v>
+        <v>-0.3700142249189168</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.7053866461753959</v>
+        <v>-0.7032609100969104</v>
       </c>
     </row>
     <row r="24">
@@ -1179,7 +1179,7 @@
         <v>-0.1891070006869582</v>
       </c>
       <c r="D24" t="n">
-        <v>0.4650466426225436</v>
+        <v>0.4650466426225434</v>
       </c>
       <c r="E24" t="n">
         <v>0.6666666666666666</v>
@@ -1188,10 +1188,10 @@
         <v>0.5081858326430231</v>
       </c>
       <c r="G24" t="n">
-        <v>0.620918713525706</v>
+        <v>0.6209187135257056</v>
       </c>
       <c r="H24" t="n">
-        <v>0.9659094619200884</v>
+        <v>0.9664101744004853</v>
       </c>
     </row>
     <row r="25">
@@ -1201,13 +1201,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6511627906976745</v>
+        <v>0.7380952380952381</v>
       </c>
       <c r="C25" t="n">
         <v>-0.1679123265606992</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.09730409846625707</v>
+        <v>-0.09730409846625705</v>
       </c>
       <c r="E25" t="n">
         <v>0.5</v>
@@ -1216,10 +1216,10 @@
         <v>1.232366664035595</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.3661841598459818</v>
+        <v>-0.3661841598459817</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.07865060563958931</v>
+        <v>-0.07713425341038704</v>
       </c>
     </row>
     <row r="26">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.4775193798449612</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="C26" t="n">
         <v>-0.2002121226750436</v>
@@ -1247,7 +1247,7 @@
         <v>-0.4177960842046977</v>
       </c>
       <c r="H26" t="n">
-        <v>0.3391734213842818</v>
+        <v>0.3402835177139619</v>
       </c>
     </row>
     <row r="27">
@@ -1263,19 +1263,19 @@
         <v>-0.2539667075870732</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1079673091236756</v>
+        <v>0.1079673091236757</v>
       </c>
       <c r="E27" t="n">
-        <v>0.4642857142857143</v>
+        <v>0.4636243386243386</v>
       </c>
       <c r="F27" t="n">
         <v>-1.707944322838364</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.005868112496669061</v>
+        <v>-0.005868112496668816</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.3024849058309488</v>
+        <v>-0.3048919658294268</v>
       </c>
     </row>
     <row r="28">
@@ -1291,7 +1291,7 @@
         <v>-0.1820048265378515</v>
       </c>
       <c r="D28" t="n">
-        <v>0.303428596432237</v>
+        <v>0.3034285964322371</v>
       </c>
       <c r="E28" t="n">
         <v>0.396551724137931</v>
@@ -1300,10 +1300,10 @@
         <v>0.7508533230397119</v>
       </c>
       <c r="G28" t="n">
-        <v>0.337228080391148</v>
+        <v>0.3372280803911481</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.726998233780079</v>
+        <v>-0.7248514844654113</v>
       </c>
     </row>
     <row r="29">
@@ -1331,7 +1331,7 @@
         <v>-3.043802353806848</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.5263192060223086</v>
+        <v>-0.5243675796150469</v>
       </c>
     </row>
     <row r="30">
@@ -1359,7 +1359,7 @@
         <v>0.3405900493690308</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.7750239840127079</v>
+        <v>-0.7728305386176354</v>
       </c>
     </row>
     <row r="31">
@@ -1369,13 +1369,13 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.7666666666666667</v>
+        <v>0.7674418604651163</v>
       </c>
       <c r="C31" t="n">
         <v>-0.205184187788136</v>
       </c>
       <c r="D31" t="n">
-        <v>0.09424688733858738</v>
+        <v>0.09424688733858737</v>
       </c>
       <c r="E31" t="n">
         <v>0.5769230769230769</v>
@@ -1384,10 +1384,10 @@
         <v>-0.04114041092304525</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.0299517791096262</v>
+        <v>-0.02995177910962622</v>
       </c>
       <c r="H31" t="n">
-        <v>0.4034540409264156</v>
+        <v>0.4045016363484769</v>
       </c>
     </row>
     <row r="32">
@@ -1397,13 +1397,13 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.7998338870431894</v>
+        <v>0.7761904761904762</v>
       </c>
       <c r="C32" t="n">
         <v>-0.184285453771279</v>
       </c>
       <c r="D32" t="n">
-        <v>0.08387376478049799</v>
+        <v>0.08387376478049793</v>
       </c>
       <c r="E32" t="n">
         <v>0.6666666666666666</v>
@@ -1412,10 +1412,10 @@
         <v>0.6729287219743062</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.04815988009496806</v>
+        <v>-0.04815988009496814</v>
       </c>
       <c r="H32" t="n">
-        <v>0.9659094619200884</v>
+        <v>0.9664101744004853</v>
       </c>
     </row>
     <row r="33">
@@ -1425,7 +1425,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.2884615384615384</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="C33" t="n">
         <v>-0.194595351118395</v>
@@ -1440,10 +1440,10 @@
         <v>0.3206595628483209</v>
       </c>
       <c r="G33" t="n">
-        <v>0.00224164337986103</v>
+        <v>0.002241643379861005</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.7053866461753959</v>
+        <v>-0.7032609100969104</v>
       </c>
     </row>
     <row r="34">
@@ -1453,7 +1453,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.2093023255813954</v>
+        <v>0.2008050089445438</v>
       </c>
       <c r="C34" t="n">
         <v>-0.2238031966272546</v>
@@ -1471,7 +1471,7 @@
         <v>1.495321218343896</v>
       </c>
       <c r="H34" t="n">
-        <v>-1.123210673199267</v>
+        <v>-1.12067868122126</v>
       </c>
     </row>
     <row r="35">
@@ -1481,25 +1481,25 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.9615384615384616</v>
+        <v>0.8837209302325582</v>
       </c>
       <c r="C35" t="n">
         <v>-0.226134911817538</v>
       </c>
       <c r="D35" t="n">
-        <v>0.3468781549400004</v>
+        <v>0.3468781549400003</v>
       </c>
       <c r="E35" t="n">
-        <v>0.9259259259259259</v>
+        <v>0.9285714285714286</v>
       </c>
       <c r="F35" t="n">
         <v>-0.7569859415269478</v>
       </c>
       <c r="G35" t="n">
-        <v>0.4134957562667132</v>
+        <v>0.413495756266713</v>
       </c>
       <c r="H35" t="n">
-        <v>2.590780678124032</v>
+        <v>2.606265703817571</v>
       </c>
     </row>
     <row r="36">
@@ -1509,7 +1509,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.2870879120879121</v>
+        <v>0.2380952380952381</v>
       </c>
       <c r="C36" t="n">
         <v>-0.222738672149269</v>
@@ -1518,16 +1518,16 @@
         <v>0.4892301648054123</v>
       </c>
       <c r="E36" t="n">
-        <v>0.325</v>
+        <v>0.3214285714285715</v>
       </c>
       <c r="F36" t="n">
         <v>-0.6409430313163919</v>
       </c>
       <c r="G36" t="n">
-        <v>0.6633684206048476</v>
+        <v>0.6633684206048475</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.175438676577251</v>
+        <v>-1.195217568922036</v>
       </c>
     </row>
     <row r="37">
@@ -1543,7 +1543,7 @@
         <v>-0.2189178803002914</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.6142141682406718</v>
+        <v>-0.6142141682406721</v>
       </c>
       <c r="E37" t="n">
         <v>0.4285714285714285</v>
@@ -1552,10 +1552,10 @@
         <v>-0.5103939980409772</v>
       </c>
       <c r="G37" t="n">
-        <v>-1.273524326520559</v>
+        <v>-1.27352432652056</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.5263192060223086</v>
+        <v>-0.5243675796150469</v>
       </c>
     </row>
     <row r="38">
@@ -1571,7 +1571,7 @@
         <v>-0.2258584547941442</v>
       </c>
       <c r="D38" t="n">
-        <v>0.2233539459840138</v>
+        <v>0.2233539459840137</v>
       </c>
       <c r="E38" t="n">
         <v>0.5348837209302325</v>
@@ -1580,10 +1580,10 @@
         <v>-0.747539942222924</v>
       </c>
       <c r="G38" t="n">
-        <v>0.1966718193846507</v>
+        <v>0.1966718193846505</v>
       </c>
       <c r="H38" t="n">
-        <v>0.1399782457101104</v>
+        <v>0.1412820221779348</v>
       </c>
     </row>
     <row r="39">
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.2012820512820513</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="C39" t="n">
         <v>-0.2418526659406501</v>
@@ -1611,7 +1611,7 @@
         <v>1.814444165194629</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.4964746326634604</v>
+        <v>-0.494552024534736</v>
       </c>
     </row>
     <row r="40">
@@ -1639,7 +1639,7 @@
         <v>1.079787174617487</v>
       </c>
       <c r="H40" t="n">
-        <v>1.889009056507711</v>
+        <v>1.888612226884512</v>
       </c>
     </row>
     <row r="41">
@@ -1649,13 +1649,13 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.643103448275862</v>
+        <v>0.7</v>
       </c>
       <c r="C41" t="n">
         <v>-0.2392060740558485</v>
       </c>
       <c r="D41" t="n">
-        <v>0.7212295494574285</v>
+        <v>0.7212295494574288</v>
       </c>
       <c r="E41" t="n">
         <v>0.6</v>
@@ -1667,7 +1667,7 @@
         <v>1.070600495674357</v>
       </c>
       <c r="H41" t="n">
-        <v>0.5480854348962173</v>
+        <v>0.5489924032761363</v>
       </c>
     </row>
     <row r="42">
@@ -1677,13 +1677,13 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.692970822281167</v>
+        <v>0.680952380952381</v>
       </c>
       <c r="C42" t="n">
         <v>-0.2246998597349494</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.5988724484970276</v>
+        <v>-0.5988724484970279</v>
       </c>
       <c r="E42" t="n">
         <v>0.7083333333333334</v>
@@ -1692,10 +1692,10 @@
         <v>-0.7079530003234276</v>
       </c>
       <c r="G42" t="n">
-        <v>-1.24659477075596</v>
+        <v>-1.246594770755961</v>
       </c>
       <c r="H42" t="n">
-        <v>1.227049478810008</v>
+        <v>1.227296281353204</v>
       </c>
     </row>
     <row r="43">
@@ -1720,10 +1720,10 @@
         <v>-0.2712739036722548</v>
       </c>
       <c r="G43" t="n">
-        <v>0.07214911180536859</v>
+        <v>0.07214911180536858</v>
       </c>
       <c r="H43" t="n">
-        <v>-1.171794862388089</v>
+        <v>-1.169215631351998</v>
       </c>
     </row>
     <row r="44">
@@ -1739,7 +1739,7 @@
         <v>-0.1611385731101388</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.01652716774940664</v>
+        <v>-0.01652716774940666</v>
       </c>
       <c r="E44" t="n">
         <v>0.6428571428571429</v>
@@ -1751,7 +1751,7 @@
         <v>-0.2243951755221257</v>
       </c>
       <c r="H44" t="n">
-        <v>0.8166865951258493</v>
+        <v>0.8173323989989325</v>
       </c>
     </row>
   </sheetData>
@@ -1812,22 +1812,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5187685627378099</v>
+        <v>0.5189787767667704</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02686927190204854</v>
+        <v>0.02785316329926477</v>
       </c>
       <c r="D2" t="n">
-        <v>19.3071313814893</v>
+        <v>18.63266915828084</v>
       </c>
       <c r="E2" t="n">
-        <v>4.678468676311012e-83</v>
+        <v>1.745959834284643e-77</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4661057575189808</v>
+        <v>0.4643875798446986</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5714313679566391</v>
+        <v>0.5735699736888422</v>
       </c>
     </row>
     <row r="3">
@@ -1837,22 +1837,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.08575529454961024</v>
+        <v>0.09564380672158018</v>
       </c>
       <c r="C3" t="n">
-        <v>0.03151690414886438</v>
+        <v>0.03123686201353519</v>
       </c>
       <c r="D3" t="n">
-        <v>2.720930144171542</v>
+        <v>3.061889080924228</v>
       </c>
       <c r="E3" t="n">
-        <v>0.006509851651876862</v>
+        <v>0.002199449383018057</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02398329751363504</v>
+        <v>0.0344206821850039</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1475272915855854</v>
+        <v>0.1568669312581565</v>
       </c>
     </row>
     <row r="4">
@@ -1862,22 +1862,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01250223475451228</v>
+        <v>0.01564928838417697</v>
       </c>
       <c r="C4" t="n">
-        <v>0.02709707263596434</v>
+        <v>0.02861166510458274</v>
       </c>
       <c r="D4" t="n">
-        <v>0.461386915202006</v>
+        <v>0.5469548286328297</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6445210375064898</v>
+        <v>0.5844097660152567</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.04060705169844367</v>
+        <v>-0.04042854475852664</v>
       </c>
       <c r="G4" t="n">
-        <v>0.06561152120746822</v>
+        <v>0.07172712152688057</v>
       </c>
     </row>
     <row r="5">
@@ -1887,22 +1887,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1604405610067644</v>
+        <v>0.160252927582874</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0323849016354711</v>
+        <v>0.03272855646202574</v>
       </c>
       <c r="D5" t="n">
-        <v>4.954177808310346</v>
+        <v>4.896425168302554</v>
       </c>
       <c r="E5" t="n">
-        <v>7.263676316355445e-07</v>
+        <v>9.759578852709117e-07</v>
       </c>
       <c r="F5" t="n">
-        <v>0.09696732015836873</v>
+        <v>0.09610613565131794</v>
       </c>
       <c r="G5" t="n">
-        <v>0.22391380185516</v>
+        <v>0.2243997195144302</v>
       </c>
     </row>
   </sheetData>

--- a/results/class_sensitivity/hsp90_class_multivariable_model.xlsx
+++ b/results/class_sensitivity/hsp90_class_multivariable_model.xlsx
@@ -470,22 +470,22 @@
         <v>43</v>
       </c>
       <c r="B2" t="n">
-        <v>0.09564380672158018</v>
+        <v>0.09564380672158021</v>
       </c>
       <c r="C2" t="n">
-        <v>0.03123686201353519</v>
+        <v>0.03123686201353522</v>
       </c>
       <c r="D2" t="n">
-        <v>0.002199449383018057</v>
+        <v>0.002199449383018066</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01564928838417697</v>
+        <v>0.0156492883841769</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5844097660152567</v>
+        <v>0.5844097660152583</v>
       </c>
       <c r="G2" t="n">
-        <v>0.160252927582874</v>
+        <v>0.1602529275828742</v>
       </c>
       <c r="H2" t="n">
         <v>9.759578852709117e-07</v>
@@ -563,7 +563,7 @@
         <v>-0.1786272139903385</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.5005747545885065</v>
+        <v>-0.5005747545885064</v>
       </c>
       <c r="E2" t="n">
         <v>0.3461538461538461</v>
@@ -619,7 +619,7 @@
         <v>-0.2094323762561981</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5621957635480654</v>
+        <v>0.5621957635480657</v>
       </c>
       <c r="E4" t="n">
         <v>0.5333333333333333</v>
@@ -628,7 +628,7 @@
         <v>-0.1862927561955771</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7914460542124914</v>
+        <v>0.7914460542124919</v>
       </c>
       <c r="H4" t="n">
         <v>0.1315746321517874</v>
@@ -647,7 +647,7 @@
         <v>-0.2595319632042399</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3126084452908053</v>
+        <v>0.3126084452908054</v>
       </c>
       <c r="E5" t="n">
         <v>0.5116279069767442</v>
@@ -656,7 +656,7 @@
         <v>-1.898098293394519</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3533416097658336</v>
+        <v>0.3533416097658337</v>
       </c>
       <c r="H5" t="n">
         <v>-0.004328828214279531</v>
@@ -675,7 +675,7 @@
         <v>-0.1656382046631881</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.07965150685765064</v>
+        <v>-0.07965150685765066</v>
       </c>
       <c r="E6" t="n">
         <v>0.7209302325581395</v>
@@ -684,7 +684,7 @@
         <v>1.310068990413297</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.3351982952847029</v>
+        <v>-0.3351982952847031</v>
       </c>
       <c r="H6" t="n">
         <v>1.306168825315653</v>
@@ -731,7 +731,7 @@
         <v>-0.2183080445642374</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5519547653573037</v>
+        <v>0.5519547653573036</v>
       </c>
       <c r="E8" t="n">
         <v>0.3333333333333333</v>
@@ -740,7 +740,7 @@
         <v>-0.4895570959155838</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7734698731538114</v>
+        <v>0.7734698731538113</v>
       </c>
       <c r="H8" t="n">
         <v>-1.12067868122126</v>
@@ -768,7 +768,7 @@
         <v>1.288639055821527</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.3659891312979859</v>
+        <v>-0.3659891312979861</v>
       </c>
       <c r="H9" t="n">
         <v>0.0132448951089185</v>
@@ -787,7 +787,7 @@
         <v>-0.2152350766343056</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3276794542214616</v>
+        <v>0.3276794542214614</v>
       </c>
       <c r="E10" t="n">
         <v>0.3765227021040974</v>
@@ -796,7 +796,7 @@
         <v>-0.3845597528527057</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3797959826919857</v>
+        <v>0.3797959826919855</v>
       </c>
       <c r="H10" t="n">
         <v>-0.8502585304928608</v>
@@ -815,7 +815,7 @@
         <v>-0.1843566503272119</v>
       </c>
       <c r="D11" t="n">
-        <v>0.146289742328352</v>
+        <v>0.1462897423283519</v>
       </c>
       <c r="E11" t="n">
         <v>0.5058139534883721</v>
@@ -824,7 +824,7 @@
         <v>0.6704960740005447</v>
       </c>
       <c r="G11" t="n">
-        <v>0.06139984176562871</v>
+        <v>0.0613998417656285</v>
       </c>
       <c r="H11" t="n">
         <v>-0.04073154081233329</v>
@@ -843,7 +843,7 @@
         <v>-0.2331316047101898</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2484970233722821</v>
+        <v>0.2484970233722822</v>
       </c>
       <c r="E12" t="n">
         <v>0.2093023255813954</v>
@@ -852,7 +852,7 @@
         <v>-0.9960493423518518</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2408058484201833</v>
+        <v>0.2408058484201834</v>
       </c>
       <c r="H12" t="n">
         <v>-1.897269883313071</v>
@@ -880,7 +880,7 @@
         <v>-0.6691982386565184</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2796214281768552</v>
+        <v>0.2796214281768553</v>
       </c>
       <c r="H13" t="n">
         <v>0.7577012888383108</v>
@@ -899,7 +899,7 @@
         <v>-0.2064610311547386</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.6171689347710508</v>
+        <v>-0.6171689347710505</v>
       </c>
       <c r="E14" t="n">
         <v>0.5666666666666667</v>
@@ -908,7 +908,7 @@
         <v>-0.08476766771765566</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.278710873490574</v>
+        <v>-1.278710873490573</v>
       </c>
       <c r="H14" t="n">
         <v>0.3402835177139619</v>
@@ -927,7 +927,7 @@
         <v>-0.2082082076743421</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.5491471363354223</v>
+        <v>-0.5491471363354224</v>
       </c>
       <c r="E15" t="n">
         <v>0.5</v>
@@ -955,7 +955,7 @@
         <v>-0.1936907867929881</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6717746308695771</v>
+        <v>0.6717746308695773</v>
       </c>
       <c r="E16" t="n">
         <v>0.7857142857142857</v>
@@ -964,7 +964,7 @@
         <v>0.3515667681829672</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9837915192232661</v>
+        <v>0.9837915192232667</v>
       </c>
       <c r="H16" t="n">
         <v>1.711799051408252</v>
@@ -983,7 +983,7 @@
         <v>-0.2090581548323149</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5223054038452978</v>
+        <v>0.5223054038452977</v>
       </c>
       <c r="E17" t="n">
         <v>0.7882059800664452</v>
@@ -992,7 +992,7 @@
         <v>-0.1735063372934399</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7214258945409773</v>
+        <v>0.7214258945409772</v>
       </c>
       <c r="H17" t="n">
         <v>1.727400213950274</v>
@@ -1039,7 +1039,7 @@
         <v>-0.1783653544666676</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2243907605925615</v>
+        <v>0.2243907605925617</v>
       </c>
       <c r="E19" t="n">
         <v>0.6470099667774087</v>
@@ -1048,7 +1048,7 @@
         <v>0.8752070118314944</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1984917559553212</v>
+        <v>0.1984917559553215</v>
       </c>
       <c r="H19" t="n">
         <v>0.8433343365689713</v>
@@ -1067,7 +1067,7 @@
         <v>-0.2272999068630794</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6352947061356089</v>
+        <v>0.6352947061356091</v>
       </c>
       <c r="E20" t="n">
         <v>0.3666666666666666</v>
@@ -1076,7 +1076,7 @@
         <v>-0.7967915585240548</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9197577483144506</v>
+        <v>0.9197577483144511</v>
       </c>
       <c r="H20" t="n">
         <v>-0.9119697956590852</v>
@@ -1104,7 +1104,7 @@
         <v>0.042647472440717</v>
       </c>
       <c r="G21" t="n">
-        <v>0.06922065205435446</v>
+        <v>0.06922065205435435</v>
       </c>
       <c r="H21" t="n">
         <v>0.7577012888383108</v>
@@ -1123,7 +1123,7 @@
         <v>-0.2357862821744499</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5200865441756434</v>
+        <v>0.5200865441756435</v>
       </c>
       <c r="E22" t="n">
         <v>0.3571428571428572</v>
@@ -1132,7 +1132,7 @@
         <v>-1.086754512985503</v>
       </c>
       <c r="G22" t="n">
-        <v>0.7175310961607284</v>
+        <v>0.7175310961607287</v>
       </c>
       <c r="H22" t="n">
         <v>-0.9716009058197063</v>
@@ -1151,7 +1151,7 @@
         <v>-0.1928960493937777</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.099486079686539</v>
+        <v>-0.09948607968653908</v>
       </c>
       <c r="E23" t="n">
         <v>0.4</v>
@@ -1160,7 +1160,7 @@
         <v>0.3787214008548575</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.3700142249189168</v>
+        <v>-0.3700142249189171</v>
       </c>
       <c r="H23" t="n">
         <v>-0.7032609100969104</v>
@@ -1179,7 +1179,7 @@
         <v>-0.1891070006869582</v>
       </c>
       <c r="D24" t="n">
-        <v>0.4650466426225434</v>
+        <v>0.4650466426225433</v>
       </c>
       <c r="E24" t="n">
         <v>0.6666666666666666</v>
@@ -1207,7 +1207,7 @@
         <v>-0.1679123265606992</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.09730409846625705</v>
+        <v>-0.09730409846625707</v>
       </c>
       <c r="E25" t="n">
         <v>0.5</v>
@@ -1216,7 +1216,7 @@
         <v>1.232366664035595</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.3661841598459817</v>
+        <v>-0.3661841598459819</v>
       </c>
       <c r="H25" t="n">
         <v>-0.07713425341038704</v>
@@ -1235,7 +1235,7 @@
         <v>-0.2002121226750436</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.1267073194426124</v>
+        <v>-0.1267073194426123</v>
       </c>
       <c r="E26" t="n">
         <v>0.5666666666666667</v>
@@ -1244,7 +1244,7 @@
         <v>0.128745392741009</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.4177960842046977</v>
+        <v>-0.4177960842046978</v>
       </c>
       <c r="H26" t="n">
         <v>0.3402835177139619</v>
@@ -1272,7 +1272,7 @@
         <v>-1.707944322838364</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.005868112496668816</v>
+        <v>-0.005868112496668891</v>
       </c>
       <c r="H27" t="n">
         <v>-0.3048919658294268</v>
@@ -1291,7 +1291,7 @@
         <v>-0.1820048265378515</v>
       </c>
       <c r="D28" t="n">
-        <v>0.3034285964322371</v>
+        <v>0.3034285964322372</v>
       </c>
       <c r="E28" t="n">
         <v>0.396551724137931</v>
@@ -1300,7 +1300,7 @@
         <v>0.7508533230397119</v>
       </c>
       <c r="G28" t="n">
-        <v>0.3372280803911481</v>
+        <v>0.3372280803911484</v>
       </c>
       <c r="H28" t="n">
         <v>-0.7248514844654113</v>
@@ -1319,7 +1319,7 @@
         <v>-0.1274662959731365</v>
       </c>
       <c r="D29" t="n">
-        <v>-1.622738393458694</v>
+        <v>-1.622738393458693</v>
       </c>
       <c r="E29" t="n">
         <v>0.4285714285714285</v>
@@ -1375,7 +1375,7 @@
         <v>-0.205184187788136</v>
       </c>
       <c r="D31" t="n">
-        <v>0.09424688733858737</v>
+        <v>0.09424688733858738</v>
       </c>
       <c r="E31" t="n">
         <v>0.5769230769230769</v>
@@ -1384,7 +1384,7 @@
         <v>-0.04114041092304525</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.02995177910962622</v>
+        <v>-0.02995177910962627</v>
       </c>
       <c r="H31" t="n">
         <v>0.4045016363484769</v>
@@ -1403,7 +1403,7 @@
         <v>-0.184285453771279</v>
       </c>
       <c r="D32" t="n">
-        <v>0.08387376478049793</v>
+        <v>0.08387376478049795</v>
       </c>
       <c r="E32" t="n">
         <v>0.6666666666666666</v>
@@ -1412,7 +1412,7 @@
         <v>0.6729287219743062</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.04815988009496814</v>
+        <v>-0.0481598800949682</v>
       </c>
       <c r="H32" t="n">
         <v>0.9664101744004853</v>
@@ -1440,7 +1440,7 @@
         <v>0.3206595628483209</v>
       </c>
       <c r="G33" t="n">
-        <v>0.002241643379861005</v>
+        <v>0.002241643379860908</v>
       </c>
       <c r="H33" t="n">
         <v>-0.7032609100969104</v>
@@ -1459,7 +1459,7 @@
         <v>-0.2238031966272546</v>
       </c>
       <c r="D34" t="n">
-        <v>0.9631921853609832</v>
+        <v>0.9631921853609831</v>
       </c>
       <c r="E34" t="n">
         <v>0.3333333333333333</v>
@@ -1487,7 +1487,7 @@
         <v>-0.226134911817538</v>
       </c>
       <c r="D35" t="n">
-        <v>0.3468781549400003</v>
+        <v>0.3468781549400004</v>
       </c>
       <c r="E35" t="n">
         <v>0.9285714285714286</v>
@@ -1496,7 +1496,7 @@
         <v>-0.7569859415269478</v>
       </c>
       <c r="G35" t="n">
-        <v>0.413495756266713</v>
+        <v>0.4134957562667132</v>
       </c>
       <c r="H35" t="n">
         <v>2.606265703817571</v>
@@ -1515,7 +1515,7 @@
         <v>-0.222738672149269</v>
       </c>
       <c r="D36" t="n">
-        <v>0.4892301648054123</v>
+        <v>0.4892301648054124</v>
       </c>
       <c r="E36" t="n">
         <v>0.3214285714285715</v>
@@ -1524,7 +1524,7 @@
         <v>-0.6409430313163919</v>
       </c>
       <c r="G36" t="n">
-        <v>0.6633684206048475</v>
+        <v>0.6633684206048477</v>
       </c>
       <c r="H36" t="n">
         <v>-1.195217568922036</v>
@@ -1543,7 +1543,7 @@
         <v>-0.2189178803002914</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.6142141682406721</v>
+        <v>-0.614214168240672</v>
       </c>
       <c r="E37" t="n">
         <v>0.4285714285714285</v>
@@ -1627,7 +1627,7 @@
         <v>-0.2522460594059376</v>
       </c>
       <c r="D40" t="n">
-        <v>0.726463184016882</v>
+        <v>0.7264631840168821</v>
       </c>
       <c r="E40" t="n">
         <v>0.813953488372093</v>
@@ -1655,7 +1655,7 @@
         <v>-0.2392060740558485</v>
       </c>
       <c r="D41" t="n">
-        <v>0.7212295494574288</v>
+        <v>0.7212295494574282</v>
       </c>
       <c r="E41" t="n">
         <v>0.6</v>
@@ -1664,7 +1664,7 @@
         <v>-1.203602156554249</v>
       </c>
       <c r="G41" t="n">
-        <v>1.070600495674357</v>
+        <v>1.070600495674356</v>
       </c>
       <c r="H41" t="n">
         <v>0.5489924032761363</v>
@@ -1683,7 +1683,7 @@
         <v>-0.2246998597349494</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.5988724484970279</v>
+        <v>-0.5988724484970278</v>
       </c>
       <c r="E42" t="n">
         <v>0.7083333333333334</v>
@@ -1720,7 +1720,7 @@
         <v>-0.2712739036722548</v>
       </c>
       <c r="G43" t="n">
-        <v>0.07214911180536858</v>
+        <v>0.07214911180536852</v>
       </c>
       <c r="H43" t="n">
         <v>-1.169215631351998</v>
@@ -1739,7 +1739,7 @@
         <v>-0.1611385731101388</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.01652716774940666</v>
+        <v>-0.01652716774940665</v>
       </c>
       <c r="E44" t="n">
         <v>0.6428571428571429</v>
@@ -1748,7 +1748,7 @@
         <v>1.463812657319237</v>
       </c>
       <c r="G44" t="n">
-        <v>-0.2243951755221257</v>
+        <v>-0.2243951755221258</v>
       </c>
       <c r="H44" t="n">
         <v>0.8173323989989325</v>
@@ -1837,19 +1837,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.09564380672158018</v>
+        <v>0.09564380672158021</v>
       </c>
       <c r="C3" t="n">
-        <v>0.03123686201353519</v>
+        <v>0.03123686201353522</v>
       </c>
       <c r="D3" t="n">
-        <v>3.061889080924228</v>
+        <v>3.061889080924226</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002199449383018057</v>
+        <v>0.002199449383018066</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0344206821850039</v>
+        <v>0.03442068218500387</v>
       </c>
       <c r="G3" t="n">
         <v>0.1568669312581565</v>
@@ -1862,22 +1862,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01564928838417697</v>
+        <v>0.0156492883841769</v>
       </c>
       <c r="C4" t="n">
         <v>0.02861166510458274</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5469548286328297</v>
+        <v>0.5469548286328274</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5844097660152567</v>
+        <v>0.5844097660152583</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.04042854475852664</v>
+        <v>-0.0404285447585267</v>
       </c>
       <c r="G4" t="n">
-        <v>0.07172712152688057</v>
+        <v>0.0717271215268805</v>
       </c>
     </row>
     <row r="5">
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.160252927582874</v>
+        <v>0.1602529275828742</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03272855646202574</v>
+        <v>0.03272855646202577</v>
       </c>
       <c r="D5" t="n">
         <v>4.896425168302554</v>
@@ -1899,10 +1899,10 @@
         <v>9.759578852709117e-07</v>
       </c>
       <c r="F5" t="n">
-        <v>0.09610613565131794</v>
+        <v>0.09610613565131802</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2243997195144302</v>
+        <v>0.2243997195144303</v>
       </c>
     </row>
   </sheetData>
